--- a/excel_files/9.4.1.1.xlsx
+++ b/excel_files/9.4.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE5AB605-912B-4D72-A468-78056EB3042F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -146,7 +147,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -310,14 +311,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -327,7 +327,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -363,7 +363,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -387,10 +387,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="Normal 17" xfId="2"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+    <cellStyle name="Normal 17" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7" xfId="1"/>
+    <cellStyle name="Обычный 7" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -667,45 +667,40 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="40.42578125" style="1" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:14" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-    </row>
-    <row r="3" spans="1:13" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="23"/>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
+    </row>
+    <row r="3" spans="1:14" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="22"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -716,334 +711,358 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
-    </row>
-    <row r="4" spans="1:13" s="7" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="26" t="s">
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" spans="1:14" s="6" customFormat="1" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="9">
         <v>2014</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4" s="9">
         <v>2015</v>
       </c>
-      <c r="F4" s="10">
+      <c r="F4" s="9">
         <v>2016</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>2017</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="9">
         <v>2018</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>2019</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>2020</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>2021</v>
       </c>
-      <c r="L4" s="10">
+      <c r="L4" s="9">
         <v>2022</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="12" t="s">
+      <c r="N4" s="9">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="12">
         <v>302.60000000000002</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="12">
         <v>304.89999999999998</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="12">
         <v>264.3</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>248.2</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>283.60000000000002</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>251.6</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="13">
         <v>253.27664777870578</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="26">
         <v>272.60000000000002</v>
       </c>
-      <c r="L5" s="27">
+      <c r="L5" s="26">
         <v>292.19961890663211</v>
       </c>
-      <c r="M5" s="27">
+      <c r="M5" s="26">
         <v>311.65582791395695</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="21" t="s">
+      <c r="N5" s="26">
+        <v>291.60000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-    </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="D6" s="17"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <v>112.7</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="17">
         <v>121.8</v>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <v>101.3</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="16">
         <v>126.1</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="16">
         <v>91</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="16">
         <v>76.5</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>93.236077839070575</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="27">
         <v>98.1</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="27">
         <v>99.522498012012946</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="27">
         <v>119.55977988994496</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="N7" s="27">
+        <v>105.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <v>189.9</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="17">
         <v>183.1</v>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <v>163</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="16">
         <v>122.1</v>
       </c>
-      <c r="H8" s="17">
+      <c r="H8" s="16">
         <v>192.6</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="16">
         <v>175.1</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="16">
         <v>160</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="27">
         <v>174.5</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="27">
         <v>192.67712089461918</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="27">
         <v>192.09604802401199</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="N8" s="27">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="20" t="s">
+      <c r="B9" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-    </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="27"/>
+      <c r="L9" s="27"/>
+      <c r="M9" s="27"/>
+      <c r="N9" s="27"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>92.3</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="17">
         <v>95.4</v>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <v>80.599999999999994</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="16">
         <v>39</v>
       </c>
-      <c r="H10" s="17">
+      <c r="H10" s="16">
         <v>90.3</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="16">
         <v>75.5</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <v>69</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="27">
         <v>75.599999999999994</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="27">
         <v>88.011952928467494</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="27">
         <v>78.539269634817401</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="11" t="s">
+      <c r="N10" s="27">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <v>61.5</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="17">
         <v>49.9</v>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <v>47.1</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>47.1</v>
       </c>
-      <c r="H11" s="17">
+      <c r="H11" s="16">
         <v>60.7</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="16">
         <v>48</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <v>48.5</v>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="27">
         <v>55.5</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="27">
         <v>56.919430260413804</v>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="27">
         <v>60.030015007503756</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+      <c r="N11" s="27">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="24">
         <v>21.2</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="24">
         <v>20</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="18">
         <v>21.8</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="18">
         <v>19.5</v>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="18">
         <v>22.8</v>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="18">
         <v>25.5</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="18">
         <v>22.8</v>
       </c>
-      <c r="K12" s="29">
+      <c r="K12" s="28">
         <v>24.9</v>
       </c>
-      <c r="L12" s="29">
+      <c r="L12" s="28">
         <v>24.176373211436804</v>
       </c>
-      <c r="M12" s="29">
+      <c r="M12" s="28">
         <v>26.013006503251628</v>
+      </c>
+      <c r="N12" s="28">
+        <v>28.5</v>
       </c>
     </row>
   </sheetData>
